--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099D7CED-2CB8-4C2A-BB82-3FAFF9FADDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92466CE3-E668-4028-9B86-710293565E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
   <si>
     <t>43040909</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>disponible</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12DFFF7-5A5C-45FB-B6E9-098F577AEE4D}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -1022,6 +1025,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92466CE3-E668-4028-9B86-710293565E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719FB963-CE07-4FBE-A413-2AAF465D45BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -289,14 +289,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -664,7 +664,7 @@
       <c r="E1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>55</v>
       </c>
       <c r="G1" s="7"/>
@@ -686,13 +686,13 @@
       <c r="C2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="11">
         <v>8.4700000000000006</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>9</v>
       </c>
     </row>
@@ -706,13 +706,13 @@
       <c r="C3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="11">
         <v>8.76</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>10</v>
       </c>
     </row>
@@ -726,13 +726,13 @@
       <c r="C4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
         <v>6.8</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>30</v>
       </c>
     </row>
@@ -746,13 +746,13 @@
       <c r="C5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <v>6.53</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>6</v>
       </c>
     </row>
@@ -766,13 +766,13 @@
       <c r="C6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="11">
         <v>4.4000000000000004</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>2</v>
       </c>
     </row>
@@ -786,13 +786,13 @@
       <c r="C7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <v>4.4000000000000004</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>6</v>
       </c>
     </row>
@@ -806,13 +806,13 @@
       <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="11">
         <v>4.21</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>23</v>
       </c>
     </row>
@@ -826,14 +826,14 @@
       <c r="C9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="11">
         <v>4.26</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="11">
-        <v>2</v>
+      <c r="F9" s="10">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -846,13 +846,13 @@
       <c r="C10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="11">
         <v>4.16</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>7</v>
       </c>
     </row>
@@ -866,13 +866,13 @@
       <c r="C11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="11">
         <v>4.09</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>16</v>
       </c>
     </row>
@@ -886,13 +886,13 @@
       <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="11">
         <v>4.3100000000000005</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>3</v>
       </c>
     </row>
@@ -903,13 +903,13 @@
       <c r="C13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="11">
         <v>3.56</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>5</v>
       </c>
     </row>
@@ -917,11 +917,13 @@
       <c r="B14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="11">
+        <v>3.39</v>
+      </c>
       <c r="E14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <v>0</v>
       </c>
     </row>
@@ -935,13 +937,13 @@
       <c r="C15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="11">
         <v>4.16</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <v>15</v>
       </c>
     </row>
@@ -955,13 +957,13 @@
       <c r="C16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="11">
         <v>4.5</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <v>12</v>
       </c>
     </row>
@@ -975,13 +977,13 @@
       <c r="C17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="11">
         <v>7.62</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <v>8</v>
       </c>
     </row>
@@ -995,13 +997,13 @@
       <c r="C18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="11">
         <v>7.24</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <v>5</v>
       </c>
     </row>
@@ -1015,13 +1017,13 @@
       <c r="C19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="11">
         <v>8.81</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <v>8</v>
       </c>
     </row>

--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719FB963-CE07-4FBE-A413-2AAF465D45BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A679DC7-A644-4DAD-B31A-9B11F0753B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
@@ -292,10 +292,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -686,13 +686,13 @@
       <c r="C2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>8.4700000000000006</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <v>9</v>
       </c>
     </row>
@@ -706,13 +706,13 @@
       <c r="C3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>8.76</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>10</v>
       </c>
     </row>
@@ -726,13 +726,13 @@
       <c r="C4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>6.8</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>30</v>
       </c>
     </row>
@@ -746,13 +746,13 @@
       <c r="C5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>6.53</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>6</v>
       </c>
     </row>
@@ -766,13 +766,13 @@
       <c r="C6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>2</v>
       </c>
     </row>
@@ -786,13 +786,13 @@
       <c r="C7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>4.4000000000000004</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>6</v>
       </c>
     </row>
@@ -806,14 +806,14 @@
       <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>4.21</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
-        <v>23</v>
+      <c r="F8" s="11">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -826,13 +826,13 @@
       <c r="C9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>4.26</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>12</v>
       </c>
     </row>
@@ -846,14 +846,14 @@
       <c r="C10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>4.16</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="10">
-        <v>7</v>
+      <c r="F10" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -866,13 +866,13 @@
       <c r="C11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>4.09</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>16</v>
       </c>
     </row>
@@ -886,13 +886,13 @@
       <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>4.3100000000000005</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>3</v>
       </c>
     </row>
@@ -903,13 +903,13 @@
       <c r="C13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>3.56</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>5</v>
       </c>
     </row>
@@ -917,13 +917,13 @@
       <c r="B14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>3.39</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -937,14 +937,14 @@
       <c r="C15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>4.16</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="10">
-        <v>15</v>
+      <c r="F15" s="11">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -957,13 +957,13 @@
       <c r="C16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>4.5</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="11">
         <v>12</v>
       </c>
     </row>
@@ -977,13 +977,13 @@
       <c r="C17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>7.62</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="11">
         <v>8</v>
       </c>
     </row>
@@ -997,13 +997,13 @@
       <c r="C18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>7.24</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="11">
         <v>5</v>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
       <c r="C19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>8.81</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="11">
         <v>8</v>
       </c>
     </row>

--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A679DC7-A644-4DAD-B31A-9B11F0753B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7947FA20-4763-4441-B38E-4B1CC9F1EF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
@@ -753,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">

--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7947FA20-4763-4441-B38E-4B1CC9F1EF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CCA09-7B23-4AC0-8848-E89333266FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
+    <workbookView xWindow="23544" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -793,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -833,7 +833,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -944,7 +944,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/prix/geka.xlsx
+++ b/prix/geka.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CCA09-7B23-4AC0-8848-E89333266FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8E0303-6364-42AA-AB23-E2A388DA40AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23544" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{E54DEEA7-0B41-4DCD-A45B-352BD142BB27}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -753,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -773,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="11">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -793,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="11">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -833,7 +833,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1004,7 +1004,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1024,7 +1024,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
